--- a/data/trans_bre/IQ2601_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IQ2601_R2-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-7,94</t>
+          <t>-12,72</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-9,8%</t>
+          <t>-15,01%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 9,95</t>
+          <t>-10,25; 9,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 3,59</t>
+          <t>-16,81; 4,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 2,7</t>
+          <t>-19,06; 1,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-32,77; 18,31</t>
+          <t>-38,36; 9,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 14,2</t>
+          <t>-12,47; 13,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 7,25</t>
+          <t>-27,59; 9,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 5,04</t>
+          <t>-29,33; 2,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-36,8; 26,94</t>
+          <t>-44,5; 10,84</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,38</t>
+          <t>4,01</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 5,43</t>
+          <t>-6,16; 6,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 12,37</t>
+          <t>-3,4; 11,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 7,41</t>
+          <t>-7,33; 7,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 22,33</t>
+          <t>-13,16; 19,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 7,54</t>
+          <t>-7,97; 8,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 24,01</t>
+          <t>-5,42; 21,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 12,06</t>
+          <t>-10,87; 12,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 39,11</t>
+          <t>-17,14; 33,95</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,93</t>
+          <t>-3,96</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-3,88%</t>
+          <t>-5,29%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 10,29</t>
+          <t>-8,66; 9,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 4,79</t>
+          <t>-13,66; 5,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 9,69</t>
+          <t>-6,83; 9,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,35; 12,67</t>
+          <t>-20,57; 12,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 16,73</t>
+          <t>-12,39; 16,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 9,99</t>
+          <t>-23,37; 11,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 15,45</t>
+          <t>-9,61; 15,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 19,32</t>
+          <t>-26,2; 18,76</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-9,18</t>
+          <t>-10,28</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-12,6%</t>
+          <t>-13,97%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,01; 16,12</t>
+          <t>-0,39; 15,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,85; 25,21</t>
+          <t>8,44; 24,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 12,04</t>
+          <t>-7,18; 10,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,81; 4,6</t>
+          <t>-23,92; 5,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 36,8</t>
+          <t>-0,66; 36,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,21; 89,97</t>
+          <t>23,33; 87,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 20,94</t>
+          <t>-10,17; 17,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,65; 6,7</t>
+          <t>-30,96; 7,74</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,45</t>
+          <t>-5,31</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-4,72%</t>
+          <t>-7,24%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 6,88</t>
+          <t>-1,39; 6,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 7,87</t>
+          <t>-0,62; 7,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 3,77</t>
+          <t>-4,12; 4,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 4,71</t>
+          <t>-14,2; 3,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 10,87</t>
+          <t>-2,11; 10,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 17,02</t>
+          <t>-1,2; 16,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 5,97</t>
+          <t>-6,23; 6,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 6,9</t>
+          <t>-18,36; 5,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IQ2601_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IQ2601_R2-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-6,6</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-8,02</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-12,72</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,56%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-12,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-13,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-15,01%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-0.429614504920417</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-6.604755711793847</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-8.021035402726662</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-12.72408120312607</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.005616226668709041</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.1201334926062916</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.1337441382905066</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1500996443318253</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-10,25; 9,74</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-16,81; 4,41</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-19,06; 1,87</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-38,36; 9,22</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-12,47; 13,67</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-27,59; 9,05</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-29,33; 2,99</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-44,5; 10,84</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-10.24967439146482</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-16.81348869131418</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-19.05640004862653</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-38.36207626620482</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1247126359126147</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2759263656524599</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.2932938424501598</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4450387944928704</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>9.743016794360029</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.407017534254947</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>1.87229061517609</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>9.215095043223869</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1366842622066529</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.09052611889976564</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.02985813342755756</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.1083742732746857</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,01</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,41</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,01</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-0,75%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,19%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-6,16; 6,02</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,4; 11,41</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-7,33; 7,78</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-13,16; 19,33</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-7,97; 8,47</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-5,42; 21,94</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-10,87; 12,67</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-17,14; 33,95</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.5564060882238486</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>4.013341394834436</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.4075171133957833</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>4.0089646866033</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.007463653896686833</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.07190249080119639</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.006274800260049881</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.05914460905072367</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-3,8</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,46</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,96</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-7,29%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-5,29%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-6.155142044852973</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.396723964755754</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-7.326846538647576</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-13.16091606864157</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.07968592032812219</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.05422282117907502</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1086850534127328</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.1713610909910996</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-8,66; 9,99</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-13,66; 5,4</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,83; 9,52</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-20,57; 12,52</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-12,39; 16,47</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-23,37; 11,32</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-9,61; 15,36</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-26,2; 18,76</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>6.021895040671811</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>11.41109330545657</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.783552060024738</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>19.33344277458944</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.08470977906833266</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.2193877898774595</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.1266936283294753</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.3394596248625847</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>8,46</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>16,89</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,67</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-10,28</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,87%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>52,19%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-13,97%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.31270695445026</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-3.798407389083081</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.458877965932825</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-3.958539813068007</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.01963025525224034</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.07287954799007118</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.02179381006423046</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.05290847164088128</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,39; 15,75</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8,44; 24,89</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,18; 10,57</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-23,92; 5,36</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-0,66; 36,21</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>23,33; 87,49</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-10,17; 17,28</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-30,96; 7,74</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-8.657101441583555</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-13.66452713203588</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.832101381638149</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-20.56689846714551</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1239246128941563</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.2336734729392115</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.09607573329775716</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2619605438830961</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>9.986881979239717</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.39659215019199</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>9.518957670570765</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>12.52143987492877</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.1647086709112764</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1132497907705533</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.15358875711332</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.1875741785589562</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>8.464990926285083</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>16.88853033569194</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.669344736411494</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-10.28162151388804</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1786670244294165</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.5218694221983267</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.04202140995191496</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1396927245092416</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.3903288826122535</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>8.443969676003457</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-7.181294763697619</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-23.92149902487136</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.006626067926561184</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.2332668954246283</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1016966230801174</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3096383867853801</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>15.75429660638749</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>24.88768088231329</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>10.56842559679882</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5.359448620740105</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.3621407150438454</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.8748643882710778</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.1728215281210084</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.07742797456294392</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2,47</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3,44</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,28</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-5,31</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-0,43%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-7,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,39; 6,66</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,62; 7,84</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-4,12; 4,05</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-14,2; 3,87</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 10,35</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-1,2; 16,52</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-6,23; 6,63</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-18,36; 5,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>2.470754553104515</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.444153575392439</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.2753724849970163</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-5.313937791468581</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.0377856337824855</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.07020424893541366</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.004280419020507594</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.07242015368393805</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.390513027135787</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.6210496730051308</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-4.119367065284782</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-14.20344281858877</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.02109542185678064</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.01202439027529226</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.06231859484019749</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1836431515454182</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.655448949132801</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.837329651548314</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.054620270511721</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.872364268931698</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.1034537967837209</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1652468135290768</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.06629612987983668</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.05747434705184282</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
